--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -2950,6 +2950,35 @@
         <v>46277.4294212963</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>19.826</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="n">
+        <v>46278.46946314815</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>46278</v>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>46278.47145833333</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -2979,6 +2979,35 @@
         <v>46278.47145833333</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="n">
+        <v>46279.50656355324</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>46279</v>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v>46279.506875</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3008,6 +3008,35 @@
         <v>46279.506875</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>19.788</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="n">
+        <v>46280.46963310185</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>46280</v>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v>46280.47253472222</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3037,6 +3037,35 @@
         <v>46280.47253472222</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="n">
+        <v>46281.45963116898</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>46281</v>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>46281.46099537037</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3066,6 +3066,35 @@
         <v>46281.46099537037</v>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>19.58</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="n">
+        <v>46282.46572077546</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>46282</v>
+      </c>
+      <c r="G91" s="4" t="n">
+        <v>46282.46799768518</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3095,6 +3095,35 @@
         <v>46282.46799768518</v>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>19.661</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="n">
+        <v>46283.44465265046</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>46283</v>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>46283.44912037037</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3124,6 +3124,35 @@
         <v>46283.44912037037</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="n">
+        <v>46284.43074329861</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>46284</v>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>46284.43815972222</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3153,6 +3153,35 @@
         <v>46284.43815972222</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>19.816</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="n">
+        <v>46285.44462244213</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>46285</v>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>46285.45364583333</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3182,6 +3182,35 @@
         <v>46285.45364583333</v>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>18.546</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="n">
+        <v>46286.51149837963</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>46286</v>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>46286.51277777777</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3211,6 +3211,35 @@
         <v>46286.51277777777</v>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="n">
+        <v>46287.46545652777</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>46287</v>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>46287.46563657407</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3240,6 +3240,35 @@
         <v>46287.46563657407</v>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="n">
+        <v>46288.45704142361</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>46288</v>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>46288.45931712963</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3269,6 +3269,35 @@
         <v>46288.45931712963</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>18.595</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="n">
+        <v>46289.46969780092</v>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>46289</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>46289.4722337963</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3298,6 +3298,35 @@
         <v>46289.4722337963</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>18.21</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="n">
+        <v>46290.47370164352</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>46290</v>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>46290.47579861111</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3327,6 +3327,35 @@
         <v>46290.47579861111</v>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>18.304</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="n">
+        <v>46291.42750533565</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>46291</v>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>46291.45865740741</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3356,6 +3356,35 @@
         <v>46291.45865740741</v>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>18.304</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="n">
+        <v>46292.48576116898</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>46292</v>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>46292.48575231482</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3385,6 +3385,35 @@
         <v>46292.48575231482</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="n">
+        <v>46293.54887282407</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>46293</v>
+      </c>
+      <c r="G102" s="4" t="n">
+        <v>46293.55189814815</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3414,6 +3414,35 @@
         <v>46293.55189814815</v>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>17.61</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="n">
+        <v>46294.5154091088</v>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>46294</v>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>46294.51564814815</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3443,6 +3443,35 @@
         <v>46294.51564814815</v>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="n">
+        <v>46295.49068149306</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>46295</v>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>46295.50534722222</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3472,6 +3472,35 @@
         <v>46295.50534722222</v>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>18.641</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="n">
+        <v>46296.52791505787</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>46296</v>
+      </c>
+      <c r="G105" s="4" t="n">
+        <v>46296.52858796297</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3501,6 +3501,35 @@
         <v>46296.52858796297</v>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="n">
+        <v>46297.49892366898</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>46297</v>
+      </c>
+      <c r="G106" s="4" t="n">
+        <v>46297.50398148148</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3530,6 +3530,35 @@
         <v>46297.50398148148</v>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="n">
+        <v>46298.46935827546</v>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>46298</v>
+      </c>
+      <c r="G107" s="4" t="n">
+        <v>46298.47032407407</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3559,6 +3559,35 @@
         <v>46298.47032407407</v>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>19.18</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="n">
+        <v>46299.49010199074</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>46299</v>
+      </c>
+      <c r="G108" s="4" t="n">
+        <v>46299.49788194444</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3588,6 +3588,35 @@
         <v>46299.49788194444</v>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>18.23</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="n">
+        <v>46300.57389565972</v>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>46300</v>
+      </c>
+      <c r="G109" s="4" t="n">
+        <v>46300.58167824074</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3617,6 +3617,35 @@
         <v>46300.58167824074</v>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="n">
+        <v>46301.54068795139</v>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>46301</v>
+      </c>
+      <c r="G110" s="4" t="n">
+        <v>46301.54083333333</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3646,6 +3646,35 @@
         <v>46301.54083333333</v>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>19.103</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="n">
+        <v>46302.52809645834</v>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>46302</v>
+      </c>
+      <c r="G111" s="4" t="n">
+        <v>46302.53680555556</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3675,6 +3675,35 @@
         <v>46302.53680555556</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>19.64</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="n">
+        <v>46303.53212824074</v>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>46303</v>
+      </c>
+      <c r="G112" s="4" t="n">
+        <v>46303.54270833333</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3704,6 +3704,35 @@
         <v>46303.54270833333</v>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>19.67</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="n">
+        <v>46304.53229328704</v>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>46304</v>
+      </c>
+      <c r="G113" s="4" t="n">
+        <v>46304.53340277778</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3733,6 +3733,35 @@
         <v>46304.53340277778</v>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>19.96</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="n">
+        <v>46305.47278641204</v>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>46305</v>
+      </c>
+      <c r="G114" s="4" t="n">
+        <v>46305.50422453704</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3762,6 +3762,35 @@
         <v>46305.50422453704</v>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>19.964</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="n">
+        <v>46306.51098506944</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>46306</v>
+      </c>
+      <c r="G115" s="4" t="n">
+        <v>46306.5137962963</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3791,6 +3791,35 @@
         <v>46306.5137962963</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>208.93</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="n">
+        <v>46307.61131371528</v>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>46307</v>
+      </c>
+      <c r="G116" s="4" t="n">
+        <v>46307.61546296296</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3820,6 +3820,35 @@
         <v>46307.61546296296</v>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>216.44</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="n">
+        <v>46308.5697422338</v>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>46308</v>
+      </c>
+      <c r="G117" s="4" t="n">
+        <v>46308.57493055556</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3849,6 +3849,35 @@
         <v>46308.57493055556</v>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>210.56</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="n">
+        <v>46309.46984481481</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>46309</v>
+      </c>
+      <c r="G118" s="4" t="n">
+        <v>46309.47589120371</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3878,6 +3878,35 @@
         <v>46309.47589120371</v>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>211.9</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="n">
+        <v>46310.45710170139</v>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>46310</v>
+      </c>
+      <c r="G119" s="4" t="n">
+        <v>46310.45996527778</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3907,6 +3907,35 @@
         <v>46310.45996527778</v>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="n">
+        <v>46311.44904202547</v>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>46311</v>
+      </c>
+      <c r="G120" s="4" t="n">
+        <v>46311.4568287037</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3936,6 +3936,35 @@
         <v>46311.4568287037</v>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>216.4</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="n">
+        <v>46312.42778324074</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>46312</v>
+      </c>
+      <c r="G121" s="4" t="n">
+        <v>46312.43015046296</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3965,6 +3965,35 @@
         <v>46312.43015046296</v>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>216.4</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="n">
+        <v>46313.42783263889</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>46313</v>
+      </c>
+      <c r="G122" s="4" t="n">
+        <v>46313.44104166667</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3994,6 +3994,35 @@
         <v>46313.44104166667</v>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>217.2</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="n">
+        <v>46314.51555446759</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="G123" s="4" t="n">
+        <v>46314.52179398148</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G123"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -4023,6 +4023,35 @@
         <v>46314.52179398148</v>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="n">
+        <v>46315.45746200231</v>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="G124" s="4" t="n">
+        <v>46315.46285879629</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G124"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -4052,6 +4052,35 @@
         <v>46315.46285879629</v>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>217.2</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="n">
+        <v>46316.47398313657</v>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="G125" s="4" t="n">
+        <v>46316.47413194444</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G125"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -4081,6 +4081,35 @@
         <v>46316.47413194444</v>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>220.3</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="n">
+        <v>46317.47332840278</v>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="G126" s="4" t="n">
+        <v>46317.47399305556</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G126"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -4110,6 +4110,35 @@
         <v>46317.47399305556</v>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="n">
+        <v>230.3</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="n">
+        <v>46318.46440002315</v>
+      </c>
+      <c r="F127" s="5" t="n">
+        <v>46318</v>
+      </c>
+      <c r="G127" s="4" t="n">
+        <v>46318.46717592593</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -4139,6 +4139,35 @@
         <v>46318.46717592593</v>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>229.5</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="n">
+        <v>46319.4226199537</v>
+      </c>
+      <c r="F128" s="5" t="n">
+        <v>46319</v>
+      </c>
+      <c r="G128" s="4" t="n">
+        <v>46319.43836805555</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -4168,6 +4168,35 @@
         <v>46319.43836805555</v>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>230.84</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="n">
+        <v>46320.44428028935</v>
+      </c>
+      <c r="F129" s="5" t="n">
+        <v>46320</v>
+      </c>
+      <c r="G129" s="4" t="n">
+        <v>46320.45652777778</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -4197,6 +4197,35 @@
         <v>46320.45652777778</v>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>235.1</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="n">
+        <v>46321.51542582176</v>
+      </c>
+      <c r="F130" s="5" t="n">
+        <v>46321</v>
+      </c>
+      <c r="G130" s="4" t="n">
+        <v>46321.51994212963</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G130"/>
+  <dimension ref="A1:G131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -4226,6 +4226,35 @@
         <v>46321.51994212963</v>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>233.8</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="n">
+        <v>46322.48662984954</v>
+      </c>
+      <c r="F131" s="5" t="n">
+        <v>46322</v>
+      </c>
+      <c r="G131" s="4" t="n">
+        <v>46322.4909375</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G131"/>
+  <dimension ref="A1:G132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -4255,6 +4255,35 @@
         <v>46322.4909375</v>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>245.9</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="n">
+        <v>46323.51438881944</v>
+      </c>
+      <c r="F132" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="G132" s="4" t="n">
+        <v>46323.51464120371</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G132"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -4284,6 +4284,35 @@
         <v>46323.51464120371</v>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>241.8</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="n">
+        <v>46324.51557457176</v>
+      </c>
+      <c r="F133" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="G133" s="4" t="n">
+        <v>46324.52084490741</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G133"/>
+  <dimension ref="A1:G134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -4313,6 +4313,35 @@
         <v>46324.52084490741</v>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>255.6</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="n">
+        <v>46325.51466901621</v>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="G134" s="4" t="n">
+        <v>46325.51516203704</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_NBP_Price.xlsx
+++ b/Historico_NBP_Price.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G134"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -4342,6 +4342,35 @@
         <v>46325.51516203704</v>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>257.6</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="n">
+        <v>46326.48560571759</v>
+      </c>
+      <c r="F135" s="5" t="n">
+        <v>46326</v>
+      </c>
+      <c r="G135" s="4" t="n">
+        <v>46326.49484953703</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
